--- a/data/trans_orig/P57_AF_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2007</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>662495</t>
+          <t>662902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>723307</t>
+          <t>723954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>850128</t>
+          <t>854095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>918215</t>
+          <t>917861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1536429</t>
+          <t>1531975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1624402</t>
+          <t>1625533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>308416</t>
+          <t>307769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>369228</t>
+          <t>368821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>396898</t>
+          <t>397252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>464985</t>
+          <t>461018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>722433</t>
+          <t>721302</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>810406</t>
+          <t>814860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>940668</t>
+          <t>938488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1021540</t>
+          <t>1020549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>893044</t>
+          <t>897539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>974017</t>
+          <t>972381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1863380</t>
+          <t>1862047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1977621</t>
+          <t>1979611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670191</t>
+          <t>671182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>751063</t>
+          <t>753243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>611681</t>
+          <t>613317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>692654</t>
+          <t>688159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1299808</t>
+          <t>1297818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1414049</t>
+          <t>1415382</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285940</t>
+          <t>283932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>334807</t>
+          <t>335759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>223442</t>
+          <t>222525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>268551</t>
+          <t>265933</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>523473</t>
+          <t>522364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>589796</t>
+          <t>589821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213765</t>
+          <t>212813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262632</t>
+          <t>264640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>207861</t>
+          <t>210479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252970</t>
+          <t>253887</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>435188</t>
+          <t>435163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>501511</t>
+          <t>502620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1935520</t>
+          <t>1931499</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2047449</t>
+          <t>2040308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2009712</t>
+          <t>2014386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2120774</t>
+          <t>2124563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3977174</t>
+          <t>3970701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4128712</t>
+          <t>4129880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1224577</t>
+          <t>1231718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1336506</t>
+          <t>1340527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1256448</t>
+          <t>1252659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1367510</t>
+          <t>1362836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2520536</t>
+          <t>2519368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2672074</t>
+          <t>2678547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2012</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2012 (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>611230</t>
+          <t>608395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>673476</t>
+          <t>668937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>887310</t>
+          <t>887999</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>953344</t>
+          <t>955165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1522600</t>
+          <t>1520089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1607309</t>
+          <t>1608451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290500</t>
+          <t>295039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>352746</t>
+          <t>355581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>370181</t>
+          <t>368360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436215</t>
+          <t>435526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680192</t>
+          <t>679050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>764901</t>
+          <t>767412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1138734</t>
+          <t>1135999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1229333</t>
+          <t>1229870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1136200</t>
+          <t>1133862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1218376</t>
+          <t>1214336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2288480</t>
+          <t>2292825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2410198</t>
+          <t>2417995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>727552</t>
+          <t>727015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>818151</t>
+          <t>820886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>530726</t>
+          <t>534766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>612902</t>
+          <t>615240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1295788</t>
+          <t>1287991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1417506</t>
+          <t>1413161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>257699</t>
+          <t>254393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305535</t>
+          <t>300350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>235393</t>
+          <t>238330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>281062</t>
+          <t>281916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>503218</t>
+          <t>502475</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>570398</t>
+          <t>569673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172360</t>
+          <t>177545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>220196</t>
+          <t>223502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174220</t>
+          <t>173366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219889</t>
+          <t>216952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>362780</t>
+          <t>363505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>429960</t>
+          <t>430703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2047477</t>
+          <t>2048982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2164208</t>
+          <t>2159191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2293157</t>
+          <t>2294574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2412532</t>
+          <t>2416977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4378457</t>
+          <t>4378185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4539692</t>
+          <t>4545095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1234548</t>
+          <t>1239565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1351279</t>
+          <t>1349774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1115377</t>
+          <t>1110932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1234752</t>
+          <t>1233335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2386973</t>
+          <t>2381570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2548208</t>
+          <t>2548480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2016</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>540990</t>
+          <t>542267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>588866</t>
+          <t>588644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>776588</t>
+          <t>777714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>828223</t>
+          <t>829668</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1332888</t>
+          <t>1334853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1400060</t>
+          <t>1405095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160748</t>
+          <t>160970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>208624</t>
+          <t>207347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164282</t>
+          <t>162837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215917</t>
+          <t>214791</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>342059</t>
+          <t>337024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>409231</t>
+          <t>407266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1510615</t>
+          <t>1512117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1594641</t>
+          <t>1592951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1477532</t>
+          <t>1477003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1553575</t>
+          <t>1556200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3021563</t>
+          <t>3018491</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3130094</t>
+          <t>3131319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472967</t>
+          <t>474657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>556993</t>
+          <t>555491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423853</t>
+          <t>421228</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499896</t>
+          <t>500425</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914942</t>
+          <t>913717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023473</t>
+          <t>1026545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>341717</t>
+          <t>342373</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>387229</t>
+          <t>386739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>329974</t>
+          <t>330029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>375982</t>
+          <t>373619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>687149</t>
+          <t>687289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>750587</t>
+          <t>748778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157841</t>
+          <t>158331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203353</t>
+          <t>202697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167545</t>
+          <t>169908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>213553</t>
+          <t>213498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>338010</t>
+          <t>339819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>401448</t>
+          <t>401308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2435905</t>
+          <t>2435717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2536806</t>
+          <t>2536367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2611302</t>
+          <t>2623007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2724069</t>
+          <t>2724409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5079675</t>
+          <t>5091048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5225346</t>
+          <t>5235640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>825486</t>
+          <t>825925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>926387</t>
+          <t>926575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>789391</t>
+          <t>789051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>902158</t>
+          <t>890453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1650406</t>
+          <t>1640112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1796077</t>
+          <t>1784704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2023</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2023 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297976</t>
+          <t>298133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>340487</t>
+          <t>338647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>467260</t>
+          <t>466538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>505493</t>
+          <t>506789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>777337</t>
+          <t>779556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>834069</t>
+          <t>835296</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169000</t>
+          <t>170840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>211511</t>
+          <t>211354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>231924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271453</t>
+          <t>272175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>414131</t>
+          <t>412904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>470863</t>
+          <t>468644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>737623</t>
+          <t>705308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1281998</t>
+          <t>1278066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1183481</t>
+          <t>1161481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1579523</t>
+          <t>1551024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2066363</t>
+          <t>2077442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2700353</t>
+          <t>2689969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>993995</t>
+          <t>997927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1538370</t>
+          <t>1570685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>646731</t>
+          <t>675230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1042773</t>
+          <t>1064773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1801894</t>
+          <t>1812278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2435884</t>
+          <t>2424805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>303711</t>
+          <t>299881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>357027</t>
+          <t>354019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>288606</t>
+          <t>290152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>332301</t>
+          <t>332464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>606113</t>
+          <t>603202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>674967</t>
+          <t>676267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283266</t>
+          <t>286274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336582</t>
+          <t>340412</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325530</t>
+          <t>325367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>369225</t>
+          <t>367679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>623157</t>
+          <t>621857</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692011</t>
+          <t>694922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1352082</t>
+          <t>1383064</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1935428</t>
+          <t>1939865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1974915</t>
+          <t>1979105</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2390508</t>
+          <t>2386471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3448349</t>
+          <t>3476998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4160619</t>
+          <t>4158198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1490344</t>
+          <t>1485907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2073690</t>
+          <t>2042708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1232290</t>
+          <t>1236327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1647883</t>
+          <t>1643693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2887951</t>
+          <t>2890372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3600221</t>
+          <t>3571572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_AF_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>662902</t>
+          <t>660055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>723954</t>
+          <t>720434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>854095</t>
+          <t>850491</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>917861</t>
+          <t>919985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1531975</t>
+          <t>1537540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1625533</t>
+          <t>1627173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307769</t>
+          <t>311289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>368821</t>
+          <t>371668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>397252</t>
+          <t>395128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>461018</t>
+          <t>464622</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>721302</t>
+          <t>719662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>814860</t>
+          <t>809295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>938488</t>
+          <t>940701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1020549</t>
+          <t>1022048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>897539</t>
+          <t>895977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>972381</t>
+          <t>975341</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1862047</t>
+          <t>1864641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1979611</t>
+          <t>1973384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>671182</t>
+          <t>669683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>753243</t>
+          <t>751030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>613317</t>
+          <t>610357</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>688159</t>
+          <t>689721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1297818</t>
+          <t>1304045</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1415382</t>
+          <t>1412788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>283932</t>
+          <t>286674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>335759</t>
+          <t>334252</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>222525</t>
+          <t>222473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>265933</t>
+          <t>267526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>522364</t>
+          <t>522330</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>589821</t>
+          <t>589788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212813</t>
+          <t>214320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264640</t>
+          <t>261898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210479</t>
+          <t>208886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>253887</t>
+          <t>253939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>435163</t>
+          <t>435196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>502620</t>
+          <t>502654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1931499</t>
+          <t>1929022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2040308</t>
+          <t>2039205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2014386</t>
+          <t>2014582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2124563</t>
+          <t>2123827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3970701</t>
+          <t>3973465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4129880</t>
+          <t>4136987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1231718</t>
+          <t>1232821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1340527</t>
+          <t>1343004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1252659</t>
+          <t>1253395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1362836</t>
+          <t>1362640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2519368</t>
+          <t>2512261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2678547</t>
+          <t>2675783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>608395</t>
+          <t>609316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>668937</t>
+          <t>670083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>887999</t>
+          <t>886941</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>955165</t>
+          <t>955543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1520089</t>
+          <t>1517396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1608451</t>
+          <t>1610271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295039</t>
+          <t>293893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355581</t>
+          <t>354660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368360</t>
+          <t>367982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>435526</t>
+          <t>436584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>679050</t>
+          <t>677230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767412</t>
+          <t>770105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1135999</t>
+          <t>1136639</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1229870</t>
+          <t>1221318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1133862</t>
+          <t>1137958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1214336</t>
+          <t>1217253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2292825</t>
+          <t>2295147</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2417995</t>
+          <t>2417744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>727015</t>
+          <t>735567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>820886</t>
+          <t>820246</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>534766</t>
+          <t>531849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>615240</t>
+          <t>611144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1287991</t>
+          <t>1288242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1413161</t>
+          <t>1410839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>254393</t>
+          <t>254205</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>300350</t>
+          <t>301579</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>238330</t>
+          <t>235528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>281916</t>
+          <t>279691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502475</t>
+          <t>505146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>569673</t>
+          <t>570044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177545</t>
+          <t>176316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>223502</t>
+          <t>223690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173366</t>
+          <t>175591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216952</t>
+          <t>219754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>363505</t>
+          <t>363134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>430703</t>
+          <t>428032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2048982</t>
+          <t>2039954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2159191</t>
+          <t>2157658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2294574</t>
+          <t>2297922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2416977</t>
+          <t>2414048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4378185</t>
+          <t>4366911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4545095</t>
+          <t>4541182</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1239565</t>
+          <t>1241098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1349774</t>
+          <t>1358802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1110932</t>
+          <t>1113861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1233335</t>
+          <t>1229987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2381570</t>
+          <t>2385483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2548480</t>
+          <t>2559754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>542267</t>
+          <t>543060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>588644</t>
+          <t>590584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>777714</t>
+          <t>774927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>829668</t>
+          <t>831756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1334853</t>
+          <t>1331276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1405095</t>
+          <t>1400625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,4%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160970</t>
+          <t>159030</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>207347</t>
+          <t>206554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162837</t>
+          <t>160749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214791</t>
+          <t>217578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>337024</t>
+          <t>341494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>407266</t>
+          <t>410843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1512117</t>
+          <t>1515032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1592951</t>
+          <t>1592757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1477003</t>
+          <t>1481295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1556200</t>
+          <t>1553637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3018491</t>
+          <t>3018184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3131319</t>
+          <t>3133116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>474657</t>
+          <t>474851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>555491</t>
+          <t>552576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>421228</t>
+          <t>423791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500425</t>
+          <t>496133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>913717</t>
+          <t>911920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1026545</t>
+          <t>1026852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>342373</t>
+          <t>341136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>386739</t>
+          <t>387396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>330029</t>
+          <t>330235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>373619</t>
+          <t>373884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>687289</t>
+          <t>686115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>748778</t>
+          <t>746639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158331</t>
+          <t>157674</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202697</t>
+          <t>203934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169908</t>
+          <t>169643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>213498</t>
+          <t>213292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339819</t>
+          <t>341958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>401308</t>
+          <t>402482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2435717</t>
+          <t>2434535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2536367</t>
+          <t>2537318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2623007</t>
+          <t>2624840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2724409</t>
+          <t>2721643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5091048</t>
+          <t>5084530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5235640</t>
+          <t>5236640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>825925</t>
+          <t>824974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>926575</t>
+          <t>927757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>789051</t>
+          <t>791817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>890453</t>
+          <t>888620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1640112</t>
+          <t>1639112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1784704</t>
+          <t>1791222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>320059</t>
+          <t>362650</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>298133</t>
+          <t>341644</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>338647</t>
+          <t>384065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>487015</t>
+          <t>536410</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>466538</t>
+          <t>515309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>506789</t>
+          <t>555406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>807074</t>
+          <t>899060</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>779556</t>
+          <t>867871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>835296</t>
+          <t>927412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>189428</t>
+          <t>210452</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170840</t>
+          <t>189037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>211354</t>
+          <t>231458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>251698</t>
+          <t>266864</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231924</t>
+          <t>247868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272175</t>
+          <t>287965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>441126</t>
+          <t>477316</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>412904</t>
+          <t>448964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>468644</t>
+          <t>508505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>509487</t>
+          <t>573102</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>509487</t>
+          <t>573102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>509487</t>
+          <t>573102</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>738713</t>
+          <t>803274</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>738713</t>
+          <t>803274</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>738713</t>
+          <t>803274</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1248200</t>
+          <t>1376376</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1248200</t>
+          <t>1376376</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1248200</t>
+          <t>1376376</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1127919</t>
+          <t>1265117</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>705308</t>
+          <t>1211775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1278066</t>
+          <t>1322041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1313565</t>
+          <t>1261551</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1161481</t>
+          <t>1218939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1551024</t>
+          <t>1307115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2441483</t>
+          <t>2526668</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2077442</t>
+          <t>2458265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2689969</t>
+          <t>2596278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1148074</t>
+          <t>949436</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997927</t>
+          <t>892512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1570685</t>
+          <t>1002778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>912689</t>
+          <t>897602</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>675230</t>
+          <t>852038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1064773</t>
+          <t>940214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2060764</t>
+          <t>1847038</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1812278</t>
+          <t>1777428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2424805</t>
+          <t>1915441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2275993</t>
+          <t>2214553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2275993</t>
+          <t>2214553</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2275993</t>
+          <t>2214553</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2226254</t>
+          <t>2159153</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2226254</t>
+          <t>2159153</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2226254</t>
+          <t>2159153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4502247</t>
+          <t>4373706</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4502247</t>
+          <t>4373706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4502247</t>
+          <t>4373706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>328054</t>
+          <t>360570</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299881</t>
+          <t>332124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>354019</t>
+          <t>390328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>310868</t>
+          <t>350403</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>290152</t>
+          <t>326608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>332464</t>
+          <t>374605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>638922</t>
+          <t>710973</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>603202</t>
+          <t>675181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>676267</t>
+          <t>750085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>312239</t>
+          <t>344517</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>286274</t>
+          <t>314759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>340412</t>
+          <t>372963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>346963</t>
+          <t>380411</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325367</t>
+          <t>356209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>367679</t>
+          <t>404206</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>659202</t>
+          <t>724929</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621857</t>
+          <t>685817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>694922</t>
+          <t>760721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>640293</t>
+          <t>705087</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>640293</t>
+          <t>705087</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>640293</t>
+          <t>705087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>657831</t>
+          <t>730814</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>657831</t>
+          <t>730814</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657831</t>
+          <t>730814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1298124</t>
+          <t>1435902</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1298124</t>
+          <t>1435902</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1298124</t>
+          <t>1435902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1776030</t>
+          <t>1988338</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1383064</t>
+          <t>1919659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1939865</t>
+          <t>2054195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2111448</t>
+          <t>2148364</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1979105</t>
+          <t>2094247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2386471</t>
+          <t>2204668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3887479</t>
+          <t>4136702</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3476998</t>
+          <t>4062126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4158198</t>
+          <t>4229896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,86%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1649742</t>
+          <t>1504404</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1485907</t>
+          <t>1438547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2042708</t>
+          <t>1573083</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1511350</t>
+          <t>1544877</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1236327</t>
+          <t>1488573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1643693</t>
+          <t>1598994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3161091</t>
+          <t>3049281</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2890372</t>
+          <t>2956087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3571572</t>
+          <t>3123857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3425772</t>
+          <t>3492742</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3425772</t>
+          <t>3492742</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3425772</t>
+          <t>3492742</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3622798</t>
+          <t>3693241</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3622798</t>
+          <t>3693241</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3622798</t>
+          <t>3693241</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7048570</t>
+          <t>7185983</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7048570</t>
+          <t>7185983</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7048570</t>
+          <t>7185983</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
